--- a/RestAPI/developer_feedback/FXR90_fix_list.xlsx
+++ b/RestAPI/developer_feedback/FXR90_fix_list.xlsx
@@ -10,10 +10,12 @@
     <sheet name="0. Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="1. Fix List" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2. To Verify" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3. Work Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. Fix List'!$A$3:$M$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. Fix List'!$A$3:$O$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. To Verify'!$A$3:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Work Plan'!$A$3:$E$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -58,7 +60,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -105,6 +107,21 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -132,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -171,6 +188,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -538,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -832,10 +861,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
@@ -901,6 +927,90 @@
       <c r="B37" s="3" t="inlineStr">
         <is>
           <t>#4, #7, #14 - schema/examples only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>COMPLEXITY BREAKDOWN</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>15 items - self-contained edits, no unknowns. Includes #2, the highest-impact item on the list. Roughly half the list can be done today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>10 items - mechanical but touch many places, or need one fact confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>7 items (11 counting the merged ones) - real schema design work, or scope you cannot bound yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Where the effort actually is</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Operating Mode (#27, #28, #29, #31) = getMode.md + setMode.md + the mode schemas. That is MOST of the real work. Everything else is small by comparison.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED - SEND THIS TO MAYUR FIRST</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>8 items are blocked on others, not on you</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>#3 (what verbose excludes)  #8 (the payload)  #9 (expandAll)  #12 (MQTTGC name)  #15 (log levels)  #17 (which server)  #23 (powerNegotiation spelling)  #31 (dock door / ATR). Also #16 (strip the model enum?) and #22/#26 need dev input. Send these BEFORE starting, or you will finish the easy 15 and stall.</t>
         </is>
       </c>
     </row>
@@ -915,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -931,6 +1041,8 @@
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -940,7 +1052,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -1005,6 +1116,16 @@
       <c r="M3" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>Complexity</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>Blocked on</t>
         </is>
       </c>
     </row>
@@ -1068,6 +1189,12 @@
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr"/>
+      <c r="N4" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="O4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -1129,6 +1256,12 @@
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr"/>
+      <c r="N5" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1190,6 +1323,16 @@
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr"/>
+      <c r="N6" s="17" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="O6" s="18" t="inlineStr">
+        <is>
+          <t>MAYUR - what does verbose:true exclude?</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1251,6 +1394,12 @@
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr"/>
+      <c r="N7" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1312,6 +1461,12 @@
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr"/>
+      <c r="N8" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1373,6 +1528,12 @@
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1434,6 +1595,12 @@
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr"/>
+      <c r="N10" s="17" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="O10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -1495,6 +1662,16 @@
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr"/>
+      <c r="N11" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O11" s="18" t="inlineStr">
+        <is>
+          <t>MAYUR - the correct WebSocket payload</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -1556,6 +1733,16 @@
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr"/>
+      <c r="N12" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O12" s="18" t="inlineStr">
+        <is>
+          <t>MAYUR - what is 'expandAll'?</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -1617,6 +1804,12 @@
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr"/>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -1678,6 +1871,12 @@
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr"/>
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="O14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -1739,6 +1938,16 @@
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O15" s="18" t="inlineStr">
+        <is>
+          <t>MAYUR - exact name of 'keyboard' / 'MQTTGC'</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -1800,6 +2009,12 @@
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr"/>
+      <c r="N16" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="O16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -1861,6 +2076,12 @@
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr"/>
+      <c r="N17" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -1922,6 +2143,16 @@
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr"/>
+      <c r="N18" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O18" s="18" t="inlineStr">
+        <is>
+          <t>DEV - which log levels are real?</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -1983,6 +2214,16 @@
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr"/>
+      <c r="N19" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="O19" s="18" t="inlineStr">
+        <is>
+          <t>MAYUR - strip the other 4 models or keep?</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -2044,6 +2285,16 @@
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr"/>
+      <c r="N20" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="O20" s="18" t="inlineStr">
+        <is>
+          <t>MAYUR - which 'server'? NTP or cloud endpoint?</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -2105,6 +2356,12 @@
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr"/>
+      <c r="N21" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -2166,6 +2423,12 @@
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr"/>
+      <c r="N22" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="O22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -2227,6 +2490,12 @@
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr"/>
+      <c r="N23" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -2288,6 +2557,12 @@
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr"/>
+      <c r="N24" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="O24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -2349,6 +2624,16 @@
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr"/>
+      <c r="N25" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O25" s="18" t="inlineStr">
+        <is>
+          <t>DEV - correct powerSource values</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -2410,6 +2695,16 @@
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr"/>
+      <c r="N26" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O26" s="18" t="inlineStr">
+        <is>
+          <t>DEV - exact powerNegotiation enum spelling</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -2471,6 +2766,12 @@
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr"/>
+      <c r="N27" s="17" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="O27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -2532,6 +2833,12 @@
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr"/>
+      <c r="N28" s="17" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="O28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -2593,6 +2900,16 @@
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr"/>
+      <c r="N29" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O29" s="18" t="inlineStr">
+        <is>
+          <t>DEV - exact readerLocation name + lat/long structure</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -2654,6 +2971,12 @@
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr"/>
+      <c r="N30" s="17" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="O30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -2715,6 +3038,12 @@
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr"/>
+      <c r="N31" s="17" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="O31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -2776,6 +3105,12 @@
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr"/>
+      <c r="N32" s="17" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="O32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -2837,6 +3172,12 @@
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr"/>
+      <c r="N33" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="O33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -2898,6 +3239,16 @@
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr"/>
+      <c r="N34" s="17" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="O34" s="18" t="inlineStr">
+        <is>
+          <t>MAYUR - is 'dock door' ATR-only?</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -2959,6 +3310,12 @@
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr"/>
+      <c r="N35" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="O35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -3020,6 +3377,12 @@
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr"/>
+      <c r="N36" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -3081,6 +3444,12 @@
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr"/>
+      <c r="N37" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -3142,6 +3511,12 @@
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr"/>
+      <c r="N38" s="17" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="O38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -3203,9 +3578,15 @@
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr"/>
+      <c r="N39" s="17" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="O39" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M39"/>
+  <autoFilter ref="A3:O39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3530,4 +3911,803 @@
   <autoFilter ref="A3:F13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>WORK PLAN BY COMPLEXITY - do them in this order</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Why it is this tier</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Blocked on</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>App LED: remove blue</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Delete 'blue' from SetAppledRequest.color.enum. One word. KEEP blue in SetStackledRequest.</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Get/Set Mode example: Gen2X -&gt; Gen2</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Three examples say GEN2X. Find and replace. HIGHEST CUSTOMER IMPACT ON THE LIST - this is the one that generates SPRs.</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>inventoryProtocol enum</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>ALREADY DONE - enum is already [GEN2X, GEN2, HYBRID]. Verify and close.</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Model enum</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>FXR90 is ALREADY present. Only decision: strip the other 4 models or keep them.</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>MAYUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Remove XML</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>GetConfigResponse.xml and SetConfigMqttRequest.xml - delete two properties.</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Delete stray mode fields</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>PART A ONLY: delete component, payload, linkProfile from SetModeRequest. Part B (beams / dock door) is Complex - see below.</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Password description</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Mayur gave the exact replacement sentence at 00:19:08. Paste it.</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Password examples</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Add an rfid-adm example beside the existing admin one.</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>doNotPersist: remove BLE</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Remove BLE from the description and the persistence table.</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Control-mode note</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Add one sentence: Get Start/Stop IS supported in control mode.</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>getVersion empty fields</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Add 'currently always returns empty' to two field descriptions.</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>11+20</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Remove Stack LED</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Delete the /cloud/stack-led path and its 3 components. One fix closes two issues.</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Do-not-duplicate guardrail</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>NO EDIT AT ALL. This is a warning for items 27-31.</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Fix broken links</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Simple IF the count is small. Audit first.</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Server-delete limitation</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>One sentence - once you know which 'server' is meant.</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>MAYUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>12+34</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Remove GCP + keyboard-emulation</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Strings are scattered across EVERY connection-type description in the file. Tedious, not hard. Do both together.</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>MAYUR - exact name of MQTTGC</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>WebSocket: remove unsupported fields</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Remove verifyHost / verifyPeer. Blocked only on what 'expandAll' actually is.</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
+        <is>
+          <t>MAYUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>WebSocket payload</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Easy once Mayur sends the payload he referenced in the comment.</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>MAYUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>BLE version notes</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Touches 4 .md files. Mechanical.</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Split uap0 / mlan0 examples</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Separate the examples and add the mutual-exclusion note.</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Add AWS + Azure connectors</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Update the connector list and capabilities.endpointTypesSupported.</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>powerSource: DC -&gt; Power Brick</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>powerSource has NO enum today. Adding one is easy - you need the correct values.</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>DEV</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>powerNegotiation values</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>powerNegotiation has NO enum today. Same as above.</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="inlineStr">
+        <is>
+          <t>DEV - exact spelling</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Log levels</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Trivial edit. Blocked on which of off / fatal / trace / extra are real.</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>DEV</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>tagMetaData: add readerLocation</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Add READER_LOCATION to the enum - need the exact name and lat/long structure.</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>DEV</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>27+28+29</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>OPERATING MODE - THE BIG ONE</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>modeSpecificSettings, selects, accesses, radioStartConditions, radioStopConditions, rssiFilter, readerLocation are ALL absent from properties - several exist only inside examples. Deeply nested objects to author from scratch, on BOTH Get and Set. Plus keep antennaStopCondition distinct from radioStopConditions. Treat as one project, not three tickets. THIS IS MOST OF THE REAL EFFORT.</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Config schema completeness</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>'Include every supported parameter, remove every unsupported one' - unbounded until someone defines the supported set. Swallows 32, 33, 34.</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Network schema completeness</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Same shape as 36, for the network schema.</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>verbose flag</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Does not exist in the spec AND nobody knows what verbose:true excludes. HARD BLOCKED.</t>
+        </is>
+      </c>
+      <c r="E32" s="18" t="inlineStr">
+        <is>
+          <t>MAYUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Error-code schema</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>New schema. error_codes.json exists at repo root but is not wired in.</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Docs / schema sync</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>The umbrella item - effectively 'do all the others'.</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Replace stale examples</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Scope unknown until every example block is audited.</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Remove beams / directionality / dock door</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>PART B: removing beams and directionality is easy. Confirming dock door / ATR is not, and it is unresolved.</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>MAYUR</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:E36"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/RestAPI/developer_feedback/FXR90_fix_list.xlsx
+++ b/RestAPI/developer_feedback/FXR90_fix_list.xlsx
@@ -11,11 +11,13 @@
     <sheet name="1. Fix List" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2. To Verify" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="3. Work Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4. Verification" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. Fix List'!$A$3:$O$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. Fix List'!$A$3:$Q$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. To Verify'!$A$3:$F$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Work Plan'!$A$3:$E$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. Verification'!$A$4:$C$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +61,33 @@
       <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C5700"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -122,6 +149,11 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -149,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,6 +234,19 @@
     <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -567,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -861,7 +906,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
@@ -1011,6 +1055,114 @@
       <c r="B46" s="3" t="inlineStr">
         <is>
           <t>#3 (what verbose excludes)  #8 (the payload)  #9 (expandAll)  #12 (MQTTGC name)  #15 (log levels)  #17 (which server)  #23 (powerNegotiation spelling)  #31 (dock door / ATR). Also #16 (strip the model enum?) and #22/#26 need dev input. Send these BEFORE starting, or you will finish the easy 15 and stall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr"/>
+      <c r="B47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>VERIFICATION - 14 Jul 2026 (against the generated spec)</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>10 of 36 - #2 #4 #5 #14 #18 #19 #27 #28 #29 #33</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>2 - #24 (network fields look broad, need sign-off), #31 (directionality gone, but component/payload/linkProfile remain)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>23 of 36 - everything else</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>No edit needed</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>1 - #30 is a guardrail only</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Biggest win</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>#28 - selects, accesses, radioStartConditions, radioStopConditions, rssiFilter and filter are now REAL properties on operatingMode.v1, not example-only. With #27 and #29 that closes most of the Operating Mode project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Still blocked on Mayur</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>#3 (what verbose:true excludes)  #8 (the WebSocket payload)  #9 (expandAll)  #12/#34 (exact MQTTGC name)  #17 (which 'server')  #31 (dock door / ATR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Still blocked on dev</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>#15 (which log levels are real)  #22 (correct powerSource values)  #23 (powerNegotiation enum spelling)  #26 (exact readerLocation name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Quick wins left</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>#16 strip 4 models from the enum  #19 done  #32 delete two xml properties  #21 add an 'always empty' note  #13 paste Mayur's sentence  #31 delete 3 stray fields</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1043,6 +1195,8 @@
     <col width="26" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="42" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="95" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1128,6 +1282,16 @@
           <t>Blocked on</t>
         </is>
       </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>VERIFIED IN SPEC (14 Jul)</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>EVIDENCE IN FXR90-rest-api.yaml</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -1183,9 +1347,9 @@
           <t>00:00:14</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L4" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr"/>
@@ -1195,6 +1359,16 @@
         </is>
       </c>
       <c r="O4" s="7" t="inlineStr"/>
+      <c r="P4" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q4" s="7" t="inlineStr">
+        <is>
+          <t>info.description + externalDocs.url unchanged. No link audit done.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -1250,9 +1424,9 @@
           <t>00:05:34</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr"/>
@@ -1262,6 +1436,16 @@
         </is>
       </c>
       <c r="O5" s="7" t="inlineStr"/>
+      <c r="P5" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>All 4 examples now say GEN2 (get example + set_mode, set_mode_default_FXR90, set_mode_TAG_FOCUS). Was GEN2X.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1317,9 +1501,9 @@
           <t>00:06:24</t>
         </is>
       </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>BLOCKED - Mayur owes the list of what verbose:true excludes</t>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr"/>
@@ -1331,6 +1515,16 @@
       <c r="O6" s="18" t="inlineStr">
         <is>
           <t>MAYUR - what does verbose:true exclude?</t>
+        </is>
+      </c>
+      <c r="P6" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>No 'verbose' parameter or request body on GET /cloud/mode. BLOCKED on Mayur.</t>
         </is>
       </c>
     </row>
@@ -1388,9 +1582,9 @@
           <t>00:07:11, 00:37:46</t>
         </is>
       </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>ALREADY DONE - enum is already [GEN2X, GEN2, HYBRID] in both. Verify and close.</t>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr"/>
@@ -1400,6 +1594,16 @@
         </is>
       </c>
       <c r="O7" s="7" t="inlineStr"/>
+      <c r="P7" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>inventoryProtocol.v1.mode.enum = [GEN2X, GEN2, HYBRID].</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1455,9 +1659,9 @@
           <t>00:08:53</t>
         </is>
       </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr"/>
@@ -1467,6 +1671,16 @@
         </is>
       </c>
       <c r="O8" s="7" t="inlineStr"/>
+      <c r="P8" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>doNotPersistState.description + 'Persistence Across Reboots' table no longer mention BLE.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1522,9 +1736,9 @@
           <t>00:11:00</t>
         </is>
       </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr"/>
@@ -1534,6 +1748,16 @@
         </is>
       </c>
       <c r="O9" s="7" t="inlineStr"/>
+      <c r="P9" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>'4.0.11' appears nowhere in the spec. No firmware-version note on scanType.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1589,9 +1813,9 @@
           <t>00:12:55</t>
         </is>
       </c>
-      <c r="L10" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr"/>
@@ -1601,6 +1825,16 @@
         </is>
       </c>
       <c r="O10" s="7" t="inlineStr"/>
+      <c r="P10" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>FX9600 / FXR60 / FX7500 / ATR7000 still appear (mostly via GetVersionResponse.model.enum - see #16).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -1656,9 +1890,9 @@
           <t>00:13:37-00:15:58</t>
         </is>
       </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr"/>
@@ -1670,6 +1904,16 @@
       <c r="O11" s="18" t="inlineStr">
         <is>
           <t>MAYUR - the correct WebSocket payload</t>
+        </is>
+      </c>
+      <c r="P11" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>set_config_data_websocket example unchanged. BLOCKED - Mayur owes the payload.</t>
         </is>
       </c>
     </row>
@@ -1727,9 +1971,9 @@
           <t>00:13:48-00:14:44</t>
         </is>
       </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>Open - confirm 'expandAll'</t>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1741,6 +1985,16 @@
       <c r="O12" s="18" t="inlineStr">
         <is>
           <t>MAYUR - what is 'expandAll'?</t>
+        </is>
+      </c>
+      <c r="P12" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>options.security.verifyHost and .verifyPeer still present in SetConfigMqttRequest.</t>
         </is>
       </c>
     </row>
@@ -1798,9 +2052,9 @@
           <t>00:16:02</t>
         </is>
       </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1810,6 +2064,16 @@
         </is>
       </c>
       <c r="O13" s="7" t="inlineStr"/>
+      <c r="P13" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>No control-mode note in the PUT /cloud/start or PUT /cloud/stop descriptions.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -1865,9 +2129,9 @@
           <t>00:16:18</t>
         </is>
       </c>
-      <c r="L14" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L14" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1877,6 +2141,16 @@
         </is>
       </c>
       <c r="O14" s="7" t="inlineStr"/>
+      <c r="P14" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>/cloud/stack-led path still present, with GetStackledResponse / SetStackledRequest / SetStackledResponse.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -1932,9 +2206,9 @@
           <t>00:16:34-00:17:05</t>
         </is>
       </c>
-      <c r="L15" s="7" t="inlineStr">
-        <is>
-          <t>Open - confirm name</t>
+      <c r="L15" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1946,6 +2220,16 @@
       <c r="O15" s="18" t="inlineStr">
         <is>
           <t>MAYUR - exact name of 'keyboard' / 'MQTTGC'</t>
+        </is>
+      </c>
+      <c r="P15" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>mqtt-GCP x12 and keyboard-emulation x13 still in the spec.</t>
         </is>
       </c>
     </row>
@@ -2003,9 +2287,9 @@
           <t>00:18:46-00:19:44</t>
         </is>
       </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr"/>
@@ -2015,6 +2299,16 @@
         </is>
       </c>
       <c r="O16" s="7" t="inlineStr"/>
+      <c r="P16" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>Description still reads 'the username of the account to update through userName'. Mayur's wording not applied.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -2070,9 +2364,9 @@
           <t>00:19:53</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L17" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr"/>
@@ -2082,6 +2376,16 @@
         </is>
       </c>
       <c r="O17" s="7" t="inlineStr"/>
+      <c r="P17" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>Both examples present: set_password (admin) and set_password_rfidadm.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -2137,9 +2441,9 @@
           <t>00:21:08-00:25:46</t>
         </is>
       </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>Open - to verify</t>
+      <c r="L18" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr"/>
@@ -2151,6 +2455,16 @@
       <c r="O18" s="18" t="inlineStr">
         <is>
           <t>DEV - which log levels are real?</t>
+        </is>
+      </c>
+      <c r="P18" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>logLevel.v1 level.enum still [OFF, FATAL, ERROR, WARNING, DEBUG, INFO, TRACE, EXTRA]. BLOCKED on dev.</t>
         </is>
       </c>
     </row>
@@ -2208,9 +2522,9 @@
           <t>00:23:55-00:24:39</t>
         </is>
       </c>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>PARTLY DONE - FXR90 IS present. Decide whether to strip the other 4 models.</t>
+      <c r="L19" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr"/>
@@ -2222,6 +2536,16 @@
       <c r="O19" s="18" t="inlineStr">
         <is>
           <t>MAYUR - strip the other 4 models or keep?</t>
+        </is>
+      </c>
+      <c r="P19" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>GetVersionResponse.model.enum still [FXR90, FX7500, FX9600, ATR7000, FXR60]. Other 4 models not stripped.</t>
         </is>
       </c>
     </row>
@@ -2279,9 +2603,9 @@
           <t>00:25:56</t>
         </is>
       </c>
-      <c r="L20" s="7" t="inlineStr">
-        <is>
-          <t>Open - confirm which 'server'</t>
+      <c r="L20" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr"/>
@@ -2293,6 +2617,16 @@
       <c r="O20" s="18" t="inlineStr">
         <is>
           <t>MAYUR - which 'server'? NTP or cloud endpoint?</t>
+        </is>
+      </c>
+      <c r="P20" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>No server-deletion limitation note. BLOCKED - which 'server' is still unconfirmed.</t>
         </is>
       </c>
     </row>
@@ -2350,9 +2684,9 @@
           <t>00:27:08-00:27:52</t>
         </is>
       </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L21" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr"/>
@@ -2362,6 +2696,16 @@
         </is>
       </c>
       <c r="O21" s="7" t="inlineStr"/>
+      <c r="P21" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>uap0 and mlan0 have separate examples; no example activates both at once.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -2417,9 +2761,9 @@
           <t>00:28:23-00:28:58</t>
         </is>
       </c>
-      <c r="L22" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L22" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr"/>
@@ -2429,6 +2773,16 @@
         </is>
       </c>
       <c r="O22" s="7" t="inlineStr"/>
+      <c r="P22" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>SetAppledRequest.color.enum = [red, amber, green, off] - blue removed. SetStackledRequest correctly KEEPS blue.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -2484,9 +2838,9 @@
           <t>00:29:01-00:29:37</t>
         </is>
       </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>Open - merge with #11</t>
+      <c r="L23" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr"/>
@@ -2496,6 +2850,16 @@
         </is>
       </c>
       <c r="O23" s="7" t="inlineStr"/>
+      <c r="P23" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>Same as #11 - stack-led still in the FXR90 spec.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -2551,9 +2915,9 @@
           <t>00:30:12-00:31:43</t>
         </is>
       </c>
-      <c r="L24" s="7" t="inlineStr">
-        <is>
-          <t>Open - ticket exists</t>
+      <c r="L24" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr"/>
@@ -2563,6 +2927,16 @@
         </is>
       </c>
       <c r="O24" s="7" t="inlineStr"/>
+      <c r="P24" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>availableOsUpgrades / revertBackFirmware descriptions carry no 'currently always empty' note.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -2618,9 +2992,9 @@
           <t>00:34:28</t>
         </is>
       </c>
-      <c r="L25" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L25" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr"/>
@@ -2632,6 +3006,16 @@
       <c r="O25" s="18" t="inlineStr">
         <is>
           <t>DEV - correct powerSource values</t>
+        </is>
+      </c>
+      <c r="P25" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>GetStatusResponse.powerSource still a free-text string with NO enum. capabilities.supportedPowerSource still lists BOTH DC and POWERBRICK.</t>
         </is>
       </c>
     </row>
@@ -2689,9 +3073,9 @@
           <t>00:34:40</t>
         </is>
       </c>
-      <c r="L26" s="7" t="inlineStr">
-        <is>
-          <t>Open - confirm spelling</t>
+      <c r="L26" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr"/>
@@ -2703,6 +3087,16 @@
       <c r="O26" s="18" t="inlineStr">
         <is>
           <t>DEV - exact powerNegotiation enum spelling</t>
+        </is>
+      </c>
+      <c r="P26" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>GetStatusResponse.powerNegotiation still a free-text string with NO enum. BLOCKED on dev for exact values.</t>
         </is>
       </c>
     </row>
@@ -2760,9 +3154,9 @@
           <t>00:36:18</t>
         </is>
       </c>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L27" s="22" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr"/>
@@ -2772,6 +3166,16 @@
         </is>
       </c>
       <c r="O27" s="7" t="inlineStr"/>
+      <c r="P27" s="22" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>GetNetworkResponse / UpdateNetworkRequest now cover eth0, mlan0, bnep0, wan0, uap0 with IPv4/IPv6, 802.1X, WPA2/WPA3, psim/esim, hotspot. Looks broad - needs a field-by-field sign-off against the supported list.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -2827,9 +3231,9 @@
           <t>00:36:48-00:37:09</t>
         </is>
       </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L28" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr"/>
@@ -2839,6 +3243,16 @@
         </is>
       </c>
       <c r="O28" s="7" t="inlineStr"/>
+      <c r="P28" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>Umbrella item. Open until the rest are closed.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -2894,9 +3308,9 @@
           <t>00:39:18-00:41:54</t>
         </is>
       </c>
-      <c r="L29" s="7" t="inlineStr">
-        <is>
-          <t>Open - to verify</t>
+      <c r="L29" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr"/>
@@ -2908,6 +3322,16 @@
       <c r="O29" s="18" t="inlineStr">
         <is>
           <t>DEV - exact readerLocation name + lat/long structure</t>
+        </is>
+      </c>
+      <c r="P29" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>READER_LOCATION is NOT in the tagMetaData enum. Dev added a readerLocationMode.v1 schema but never wired it to anything, so the build now prunes it as unreachable.</t>
         </is>
       </c>
     </row>
@@ -2965,9 +3389,9 @@
           <t>00:45:27-00:53:52</t>
         </is>
       </c>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L30" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr"/>
@@ -2977,6 +3401,16 @@
         </is>
       </c>
       <c r="O30" s="7" t="inlineStr"/>
+      <c r="P30" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>modeSpecificSettings IS a property of operatingMode.v1 (oneOf inventorysettings.v1 / portalsettings.v1). Reaches both GET and PUT /cloud/mode.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -3032,9 +3466,9 @@
           <t>00:54:06-00:56:35</t>
         </is>
       </c>
-      <c r="L31" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L31" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr"/>
@@ -3044,6 +3478,16 @@
         </is>
       </c>
       <c r="O31" s="7" t="inlineStr"/>
+      <c r="P31" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>ALL now real properties of operatingMode.v1: selects, accesses, radioStartConditions, radioStopConditions, rssiFilter, filter. Previously example-only.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -3099,9 +3543,9 @@
           <t>00:55:38-00:56:03</t>
         </is>
       </c>
-      <c r="L32" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L32" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr"/>
@@ -3111,6 +3555,16 @@
         </is>
       </c>
       <c r="O32" s="7" t="inlineStr"/>
+      <c r="P32" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>antennaStopCondition and radioStartConditions / radioStopConditions coexist as separate properties. Not conflated.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -3166,9 +3620,9 @@
           <t>00:54:32-00:56:28</t>
         </is>
       </c>
-      <c r="L33" s="7" t="inlineStr">
-        <is>
-          <t>Open - guardrail for #27/#28</t>
+      <c r="L33" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr"/>
@@ -3178,6 +3632,16 @@
         </is>
       </c>
       <c r="O33" s="7" t="inlineStr"/>
+      <c r="P33" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q33" s="7" t="inlineStr">
+        <is>
+          <t>Guardrail, no edit required. Confirmed all 5 still present: transmitPower, antennaStopCondition, query, delayBetweenAntennaCycles, reportFilter.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -3233,9 +3697,9 @@
           <t>00:42:29, 00:48:02, 01:02:00</t>
         </is>
       </c>
-      <c r="L34" s="7" t="inlineStr">
-        <is>
-          <t>Open - confirm dock door</t>
+      <c r="L34" s="22" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr"/>
@@ -3247,6 +3711,16 @@
       <c r="O34" s="18" t="inlineStr">
         <is>
           <t>MAYUR - is 'dock door' ATR-only?</t>
+        </is>
+      </c>
+      <c r="P34" s="22" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="Q34" s="7" t="inlineStr">
+        <is>
+          <t>DONE: directionality.v1 deleted; type.enum = [SIMPLE, INVENTORY, PORTAL, CONVEYOR, CUSTOM]. NOT DONE: stray component / payload / linkProfile still in SetModeRequest allOf, labelled 'legacy fields accepted by set_mode'.</t>
         </is>
       </c>
     </row>
@@ -3304,9 +3778,9 @@
           <t>00:56:46-01:00:36</t>
         </is>
       </c>
-      <c r="L35" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L35" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr"/>
@@ -3316,6 +3790,16 @@
         </is>
       </c>
       <c r="O35" s="7" t="inlineStr"/>
+      <c r="P35" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q35" s="7" t="inlineStr">
+        <is>
+          <t>GetConfigResponse.xml and SetConfigMqttRequest.xml both still present.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -3371,9 +3855,9 @@
           <t>00:59:21-01:00:48</t>
         </is>
       </c>
-      <c r="L36" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L36" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr"/>
@@ -3383,6 +3867,16 @@
         </is>
       </c>
       <c r="O36" s="7" t="inlineStr"/>
+      <c r="P36" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="Q36" s="7" t="inlineStr">
+        <is>
+          <t>mqtt-AWS and mqtt-Azure are documented connection types; AWS_IOT_CORE and AZURE_IOT_HUB appear in capabilities.endpointTypesSupported.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -3438,9 +3932,9 @@
           <t>01:00:56</t>
         </is>
       </c>
-      <c r="L37" s="7" t="inlineStr">
-        <is>
-          <t>Open - merge with #12</t>
+      <c r="L37" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr"/>
@@ -3450,6 +3944,16 @@
         </is>
       </c>
       <c r="O37" s="7" t="inlineStr"/>
+      <c r="P37" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q37" s="7" t="inlineStr">
+        <is>
+          <t>Same as #12 - mqtt-GCP still throughout SetImportcloudconfigRequest, incl. the keyAlgorithm 'GCP connections' descriptions.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -3505,9 +4009,9 @@
           <t>01:01:09</t>
         </is>
       </c>
-      <c r="L38" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L38" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr"/>
@@ -3517,6 +4021,16 @@
         </is>
       </c>
       <c r="O38" s="7" t="inlineStr"/>
+      <c r="P38" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q38" s="7" t="inlineStr">
+        <is>
+          <t>No error-code schema in components. error_codes.json still unwired.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -3572,9 +4086,9 @@
           <t>01:01:43-01:02:05</t>
         </is>
       </c>
-      <c r="L39" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="L39" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr"/>
@@ -3584,9 +4098,19 @@
         </is>
       </c>
       <c r="O39" s="7" t="inlineStr"/>
+      <c r="P39" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="Q39" s="7" t="inlineStr">
+        <is>
+          <t>Umbrella over #32/#33/#34. Open while XML and GCP remain.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O39"/>
+  <autoFilter ref="A3:Q39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4710,4 +5234,595 @@
   <autoFilter ref="A3:E36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="120" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>VERIFICATION RUN - 14 Jul 2026, against RestAPI/FXR90-rest-api.yaml</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Source: RestDeveloperfile.yaml (developer's openAPISpecnew.yaml) -&gt; built by RestAPI/scripts/build_fxr90_rest_api.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Evidence in the generated spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>info.description + externalDocs.url unchanged. No link audit done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>All 4 examples now say GEN2 (get example + set_mode, set_mode_default_FXR90, set_mode_TAG_FOCUS). Was GEN2X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>No 'verbose' parameter or request body on GET /cloud/mode. BLOCKED on Mayur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>inventoryProtocol.v1.mode.enum = [GEN2X, GEN2, HYBRID].</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>doNotPersistState.description + 'Persistence Across Reboots' table no longer mention BLE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>'4.0.11' appears nowhere in the spec. No firmware-version note on scanType.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>FX9600 / FXR60 / FX7500 / ATR7000 still appear (mostly via GetVersionResponse.model.enum - see #16).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>set_config_data_websocket example unchanged. BLOCKED - Mayur owes the payload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>options.security.verifyHost and .verifyPeer still present in SetConfigMqttRequest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>No control-mode note in the PUT /cloud/start or PUT /cloud/stop descriptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>/cloud/stack-led path still present, with GetStackledResponse / SetStackledRequest / SetStackledResponse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>mqtt-GCP x12 and keyboard-emulation x13 still in the spec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Description still reads 'the username of the account to update through userName'. Mayur's wording not applied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Both examples present: set_password (admin) and set_password_rfidadm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>logLevel.v1 level.enum still [OFF, FATAL, ERROR, WARNING, DEBUG, INFO, TRACE, EXTRA]. BLOCKED on dev.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>GetVersionResponse.model.enum still [FXR90, FX7500, FX9600, ATR7000, FXR60]. Other 4 models not stripped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>No server-deletion limitation note. BLOCKED - which 'server' is still unconfirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>uap0 and mlan0 have separate examples; no example activates both at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>SetAppledRequest.color.enum = [red, amber, green, off] - blue removed. SetStackledRequest correctly KEEPS blue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Same as #11 - stack-led still in the FXR90 spec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>availableOsUpgrades / revertBackFirmware descriptions carry no 'currently always empty' note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>GetStatusResponse.powerSource still a free-text string with NO enum. capabilities.supportedPowerSource still lists BOTH DC and POWERBRICK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>GetStatusResponse.powerNegotiation still a free-text string with NO enum. BLOCKED on dev for exact values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>GetNetworkResponse / UpdateNetworkRequest now cover eth0, mlan0, bnep0, wan0, uap0 with IPv4/IPv6, 802.1X, WPA2/WPA3, psim/esim, hotspot. Looks broad - needs a field-by-field sign-off against the supported list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Umbrella item. Open until the rest are closed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>READER_LOCATION is NOT in the tagMetaData enum. Dev added a readerLocationMode.v1 schema but never wired it to anything, so the build now prunes it as unreachable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>modeSpecificSettings IS a property of operatingMode.v1 (oneOf inventorysettings.v1 / portalsettings.v1). Reaches both GET and PUT /cloud/mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>ALL now real properties of operatingMode.v1: selects, accesses, radioStartConditions, radioStopConditions, rssiFilter, filter. Previously example-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>antennaStopCondition and radioStartConditions / radioStopConditions coexist as separate properties. Not conflated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Guardrail, no edit required. Confirmed all 5 still present: transmitPower, antennaStopCondition, query, delayBetweenAntennaCycles, reportFilter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>DONE: directionality.v1 deleted; type.enum = [SIMPLE, INVENTORY, PORTAL, CONVEYOR, CUSTOM]. NOT DONE: stray component / payload / linkProfile still in SetModeRequest allOf, labelled 'legacy fields accepted by set_mode'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>GetConfigResponse.xml and SetConfigMqttRequest.xml both still present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>mqtt-AWS and mqtt-Azure are documented connection types; AWS_IOT_CORE and AZURE_IOT_HUB appear in capabilities.endpointTypesSupported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Same as #12 - mqtt-GCP still throughout SetImportcloudconfigRequest, incl. the keyAlgorithm 'GCP connections' descriptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>No error-code schema in components. error_codes.json still unwired.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>NOT FIXED</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Umbrella over #32/#33/#34. Open while XML and GCP remain.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:C40"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>